--- a/artifacts/correct_responses/qwen14b_rag_kimi_judge/all_runs_metrics.xlsx
+++ b/artifacts/correct_responses/qwen14b_rag_kimi_judge/all_runs_metrics.xlsx
@@ -506,7 +506,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0556</v>
+        <v>0.1111</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>32.0523076923077</v>
+        <v>33.33307692307692</v>
       </c>
     </row>
     <row r="3">
@@ -604,26 +604,26 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>76.92307692307692</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="6">
@@ -643,10 +643,10 @@
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>0.3833</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>22.30692307692307</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="7">
@@ -674,7 +674,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
@@ -684,16 +684,16 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>53.84615384615385</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="8">
@@ -713,7 +713,7 @@
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>30.76923076923077</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="9">
@@ -744,26 +744,26 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>100</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="10">
@@ -779,7 +779,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
@@ -789,16 +789,16 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>53.84615384615385</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="11">
@@ -849,26 +849,26 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>59.61538461538461</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="13">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
@@ -1139,16 +1139,16 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>53.84615384615385</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="21">
@@ -1203,10 +1203,10 @@
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4615</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>41.41923076923077</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="23">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>15.38384615384615</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="26">
@@ -1378,10 +1378,10 @@
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>38.46076923076923</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="28">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>30.76923076923077</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="30">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
@@ -1489,16 +1489,16 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>53.84615384615385</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="31">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>30.76923076923077</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="33">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
@@ -1874,16 +1874,16 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>30.76923076923077</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="42">
@@ -2214,26 +2214,26 @@
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>59.61538461538461</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
   </sheetData>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>0.186666</v>
+        <v>0.016666</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>0.199332</v>
+        <v>0.04</v>
       </c>
       <c r="F2" t="n">
-        <v>0.047008</v>
+        <v>0.002222</v>
       </c>
       <c r="G2" t="n">
-        <v>0.186666</v>
+        <v>0.016666</v>
       </c>
       <c r="H2" t="n">
-        <v>0.813334</v>
+        <v>0.9833339999999999</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>21.99243076923077</v>
+        <v>9.435861538461539</v>
       </c>
     </row>
   </sheetData>
